--- a/JavaGovna/danila/fsd-project-econ-parser/src/test/resources/ФСД_ИП+стройка.xlsx
+++ b/JavaGovna/danila/fsd-project-econ-parser/src/test/resources/ФСД_ИП+стройка.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vlads\Desktop\Учеба и Работа\Работа\Вниигаз\Модуль_экономика\JavaGovna\danila\fsd-invest-program-parser\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work_Project\JavaGovna\danila\fsd-project-econ-parser\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642B1543-45DB-4796-9AFF-51A58478E730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E28777-5616-4653-B07E-E921ADB751C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3360" yWindow="1665" windowWidth="21600" windowHeight="13635" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
@@ -28,12 +28,21 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="629">
   <si>
     <t xml:space="preserve">ГДО </t>
   </si>
@@ -1929,7 +1938,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1971,6 +1980,13 @@
     <font>
       <sz val="11"/>
       <color theme="6" tint="0.39997558519241921"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -2126,11 +2142,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Лист1"/>
       <sheetName val="Справочник"/>
@@ -2407,24 +2420,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:Q37"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="45.54296875" customWidth="1"/>
-    <col min="3" max="4" width="42.81640625" customWidth="1"/>
-    <col min="5" max="6" width="31.453125" customWidth="1"/>
-    <col min="7" max="7" width="27.26953125" customWidth="1"/>
-    <col min="8" max="8" width="51.54296875" customWidth="1"/>
-    <col min="9" max="10" width="40.54296875" customWidth="1"/>
-    <col min="11" max="11" width="14.26953125" customWidth="1"/>
+    <col min="2" max="2" width="45.5703125" customWidth="1"/>
+    <col min="3" max="4" width="42.85546875" customWidth="1"/>
+    <col min="5" max="6" width="31.42578125" customWidth="1"/>
+    <col min="7" max="7" width="27.28515625" customWidth="1"/>
+    <col min="8" max="8" width="51.5703125" customWidth="1"/>
+    <col min="9" max="10" width="40.5703125" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="12.453125" customWidth="1"/>
-    <col min="14" max="14" width="15.7265625" customWidth="1"/>
-    <col min="15" max="15" width="19.453125" customWidth="1"/>
-    <col min="16" max="16" width="36.7265625" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
+    <col min="14" max="14" width="15.7109375" customWidth="1"/>
+    <col min="15" max="15" width="19.42578125" customWidth="1"/>
+    <col min="16" max="16" width="36.7109375" customWidth="1"/>
     <col min="17" max="17" width="64" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
@@ -2433,14 +2446,14 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="14"/>
       <c r="J2" s="14"/>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
@@ -2448,7 +2461,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>0</v>
       </c>
@@ -2456,7 +2469,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
@@ -2464,26 +2477,26 @@
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>142</v>
       </c>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>143</v>
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="17"/>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
         <v>127</v>
       </c>
@@ -2529,7 +2542,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:17" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="25"/>
       <c r="C10" s="24"/>
       <c r="D10" s="24"/>
@@ -2555,7 +2568,7 @@
       <c r="P10" s="24"/>
       <c r="Q10" s="24"/>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>625</v>
       </c>
@@ -2605,19 +2618,15 @@
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>129</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>120</v>
-      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="7" t="s">
         <v>7</v>
       </c>
@@ -2653,7 +2662,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="13" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B13" s="3"/>
       <c r="C13" s="23" t="str">
         <f>IFERROR(VLOOKUP(B13,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -2676,7 +2685,7 @@
       <c r="P13" s="7"/>
       <c r="Q13" s="18"/>
     </row>
-    <row r="14" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B14" s="3"/>
       <c r="C14" s="23" t="str">
         <f>IFERROR(VLOOKUP(B14,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -2699,7 +2708,7 @@
       <c r="P14" s="7"/>
       <c r="Q14" s="18"/>
     </row>
-    <row r="15" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B15" s="3"/>
       <c r="C15" s="23" t="str">
         <f>IFERROR(VLOOKUP(B15,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -2722,7 +2731,7 @@
       <c r="P15" s="7"/>
       <c r="Q15" s="18"/>
     </row>
-    <row r="16" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="3"/>
       <c r="C16" s="23" t="str">
         <f>IFERROR(VLOOKUP(B16,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -2745,7 +2754,7 @@
       <c r="P16" s="7"/>
       <c r="Q16" s="18"/>
     </row>
-    <row r="17" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" s="3"/>
       <c r="C17" s="23" t="str">
         <f>IFERROR(VLOOKUP(B17,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -2768,7 +2777,7 @@
       <c r="P17" s="7"/>
       <c r="Q17" s="18"/>
     </row>
-    <row r="18" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B18" s="3"/>
       <c r="C18" s="23" t="str">
         <f>IFERROR(VLOOKUP(B18,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -2791,7 +2800,7 @@
       <c r="P18" s="7"/>
       <c r="Q18" s="18"/>
     </row>
-    <row r="19" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B19" s="3"/>
       <c r="C19" s="23" t="str">
         <f>IFERROR(VLOOKUP(B19,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -2814,7 +2823,7 @@
       <c r="P19" s="7"/>
       <c r="Q19" s="18"/>
     </row>
-    <row r="20" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B20" s="3"/>
       <c r="C20" s="23" t="str">
         <f>IFERROR(VLOOKUP(B20,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -2837,7 +2846,7 @@
       <c r="P20" s="7"/>
       <c r="Q20" s="18"/>
     </row>
-    <row r="21" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B21" s="3"/>
       <c r="C21" s="23" t="str">
         <f>IFERROR(VLOOKUP(B21,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -2860,7 +2869,7 @@
       <c r="P21" s="7"/>
       <c r="Q21" s="18"/>
     </row>
-    <row r="22" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B22" s="3"/>
       <c r="C22" s="23" t="str">
         <f>IFERROR(VLOOKUP(B22,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -2883,7 +2892,7 @@
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
     </row>
-    <row r="23" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B23" s="3"/>
       <c r="C23" s="23" t="str">
         <f>IFERROR(VLOOKUP(B23,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -2904,7 +2913,7 @@
       <c r="P23" s="2"/>
       <c r="Q23" s="2"/>
     </row>
-    <row r="24" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B24" s="3"/>
       <c r="C24" s="23" t="str">
         <f>IFERROR(VLOOKUP(B24,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -2925,7 +2934,7 @@
       <c r="P24" s="2"/>
       <c r="Q24" s="2"/>
     </row>
-    <row r="25" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B25" s="3"/>
       <c r="C25" s="23" t="str">
         <f>IFERROR(VLOOKUP(B25,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -2946,7 +2955,7 @@
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
     </row>
-    <row r="26" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B26" s="3"/>
       <c r="C26" s="23" t="str">
         <f>IFERROR(VLOOKUP(B26,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -2967,7 +2976,7 @@
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
     </row>
-    <row r="27" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B27" s="3"/>
       <c r="C27" s="23" t="str">
         <f>IFERROR(VLOOKUP(B27,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -2988,7 +2997,7 @@
       <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
     </row>
-    <row r="28" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B28" s="3"/>
       <c r="C28" s="23" t="str">
         <f>IFERROR(VLOOKUP(B28,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -3009,7 +3018,7 @@
       <c r="P28" s="2"/>
       <c r="Q28" s="2"/>
     </row>
-    <row r="29" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B29" s="3"/>
       <c r="C29" s="23" t="str">
         <f>IFERROR(VLOOKUP(B29,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -3030,7 +3039,7 @@
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
     </row>
-    <row r="30" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B30" s="3"/>
       <c r="C30" s="23" t="str">
         <f>IFERROR(VLOOKUP(B30,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -3051,7 +3060,7 @@
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
     </row>
-    <row r="31" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B31" s="3"/>
       <c r="C31" s="23" t="str">
         <f>IFERROR(VLOOKUP(B31,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -3072,7 +3081,7 @@
       <c r="P31" s="2"/>
       <c r="Q31" s="2"/>
     </row>
-    <row r="32" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B32" s="3"/>
       <c r="C32" s="23" t="str">
         <f>IFERROR(VLOOKUP(B32,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -3093,7 +3102,7 @@
       <c r="P32" s="2"/>
       <c r="Q32" s="2"/>
     </row>
-    <row r="33" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B33" s="3"/>
       <c r="C33" s="23" t="str">
         <f>IFERROR(VLOOKUP(B33,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -3114,7 +3123,7 @@
       <c r="P33" s="2"/>
       <c r="Q33" s="2"/>
     </row>
-    <row r="34" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B34" s="3"/>
       <c r="C34" s="23" t="str">
         <f>IFERROR(VLOOKUP(B34,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -3135,7 +3144,7 @@
       <c r="P34" s="2"/>
       <c r="Q34" s="2"/>
     </row>
-    <row r="35" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B35" s="3"/>
       <c r="C35" s="23" t="str">
         <f>IFERROR(VLOOKUP(B35,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -3156,7 +3165,7 @@
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
     </row>
-    <row r="36" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B36" s="3"/>
       <c r="C36" s="23" t="str">
         <f>IFERROR(VLOOKUP(B36,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -3177,7 +3186,7 @@
       <c r="P36" s="2"/>
       <c r="Q36" s="2"/>
     </row>
-    <row r="37" spans="2:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B37" s="3"/>
       <c r="C37" s="23" t="str">
         <f>IFERROR(VLOOKUP(B37,Справочник!$H:$I,2,FALSE),"Необходимо внести наименование проекта на лист Справочник")</f>
@@ -3215,6 +3224,7 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="F9:F10"/>
   </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Месторождение</formula1>
@@ -3294,32 +3304,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:U235"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="9"/>
-    <col min="2" max="2" width="45.7265625" style="9" customWidth="1"/>
-    <col min="3" max="4" width="9.1796875" style="9"/>
-    <col min="5" max="5" width="37.26953125" style="9" customWidth="1"/>
-    <col min="6" max="6" width="10.7265625" style="9" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="9"/>
+    <col min="2" max="2" width="45.7109375" style="9" customWidth="1"/>
+    <col min="3" max="4" width="9.140625" style="9"/>
+    <col min="5" max="5" width="37.28515625" style="9" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="9" customWidth="1"/>
     <col min="7" max="7" width="31" style="21" customWidth="1"/>
-    <col min="8" max="8" width="30.7265625" style="21" customWidth="1"/>
-    <col min="9" max="9" width="42.7265625" style="21" customWidth="1"/>
-    <col min="10" max="10" width="9.1796875" style="9"/>
-    <col min="11" max="11" width="36.81640625" style="9" customWidth="1"/>
-    <col min="12" max="12" width="9.1796875" style="9"/>
-    <col min="13" max="13" width="36.7265625" style="9" customWidth="1"/>
-    <col min="14" max="14" width="9.1796875" style="9"/>
-    <col min="15" max="15" width="27.1796875" style="9" customWidth="1"/>
-    <col min="16" max="16" width="9.1796875" style="9"/>
+    <col min="8" max="8" width="30.7109375" style="21" customWidth="1"/>
+    <col min="9" max="9" width="42.7109375" style="21" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="9"/>
+    <col min="11" max="11" width="36.85546875" style="9" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" style="9"/>
+    <col min="13" max="13" width="36.7109375" style="9" customWidth="1"/>
+    <col min="14" max="14" width="9.140625" style="9"/>
+    <col min="15" max="15" width="27.140625" style="9" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" style="9"/>
     <col min="17" max="17" width="37" style="9" customWidth="1"/>
-    <col min="18" max="18" width="9.1796875" style="9"/>
-    <col min="19" max="19" width="31.54296875" style="9" customWidth="1"/>
-    <col min="20" max="20" width="9.1796875" style="9"/>
-    <col min="21" max="21" width="27.26953125" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="9.1796875" style="9"/>
+    <col min="18" max="18" width="9.140625" style="9"/>
+    <col min="19" max="19" width="31.5703125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="9.140625" style="9"/>
+    <col min="21" max="21" width="27.28515625" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" ht="42" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:21" ht="45" x14ac:dyDescent="0.2">
       <c r="B2" s="10" t="s">
         <v>12</v>
       </c>
@@ -3358,7 +3368,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="12" t="s">
         <v>30</v>
       </c>
@@ -3397,7 +3407,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:21" ht="45" x14ac:dyDescent="0.25">
       <c r="B4" s="12" t="s">
         <v>139</v>
       </c>
@@ -3436,7 +3446,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:21" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:21" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
         <v>25</v>
       </c>
@@ -3469,7 +3479,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="6" spans="2:21" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:21" ht="45" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
         <v>38</v>
       </c>
@@ -3496,7 +3506,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="7" spans="2:21" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:21" ht="75" x14ac:dyDescent="0.25">
       <c r="B7" s="12" t="s">
         <v>23</v>
       </c>
@@ -3520,7 +3530,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="8" spans="2:21" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:21" ht="45" x14ac:dyDescent="0.25">
       <c r="B8" s="12" t="s">
         <v>44</v>
       </c>
@@ -3541,7 +3551,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="9" spans="2:21" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:21" ht="45" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
         <v>18</v>
       </c>
@@ -3562,7 +3572,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="10" spans="2:21" ht="58" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:21" ht="60" x14ac:dyDescent="0.25">
       <c r="B10" s="12" t="s">
         <v>10</v>
       </c>
@@ -3583,7 +3593,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="11" spans="2:21" ht="29" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:21" ht="30" x14ac:dyDescent="0.25">
       <c r="B11" s="12" t="s">
         <v>21</v>
       </c>
@@ -3604,7 +3614,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="12" spans="2:21" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:21" ht="45" x14ac:dyDescent="0.25">
       <c r="B12" s="12" t="s">
         <v>32</v>
       </c>
@@ -3625,7 +3635,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="13" spans="2:21" ht="58" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:21" ht="60" x14ac:dyDescent="0.25">
       <c r="B13" s="12" t="s">
         <v>16</v>
       </c>
@@ -3646,7 +3656,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B14" s="12" t="s">
         <v>42</v>
       </c>
@@ -3667,7 +3677,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="15" spans="2:21" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:21" ht="30" x14ac:dyDescent="0.25">
       <c r="B15" s="12" t="s">
         <v>14</v>
       </c>
@@ -3688,7 +3698,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="16" spans="2:21" ht="58" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:21" ht="60" x14ac:dyDescent="0.25">
       <c r="B16" s="12" t="s">
         <v>40</v>
       </c>
@@ -3709,7 +3719,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:9" ht="45" x14ac:dyDescent="0.25">
       <c r="B17" s="12" t="s">
         <v>36</v>
       </c>
@@ -3730,7 +3740,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="58" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:9" ht="60" x14ac:dyDescent="0.25">
       <c r="B18" s="12" t="s">
         <v>28</v>
       </c>
@@ -3751,7 +3761,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:9" ht="45" x14ac:dyDescent="0.25">
       <c r="B19" s="12" t="s">
         <v>34</v>
       </c>
@@ -3772,7 +3782,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:9" ht="45" x14ac:dyDescent="0.25">
       <c r="B20" s="12" t="s">
         <v>140</v>
       </c>
@@ -3793,7 +3803,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:9" ht="45" x14ac:dyDescent="0.25">
       <c r="B21" s="12"/>
       <c r="D21" s="9" t="s">
         <v>23</v>
@@ -3812,7 +3822,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:9" ht="60" x14ac:dyDescent="0.25">
       <c r="B22" s="12"/>
       <c r="D22" s="9" t="s">
         <v>23</v>
@@ -3831,7 +3841,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:9" ht="60" x14ac:dyDescent="0.25">
       <c r="D23" s="9" t="s">
         <v>23</v>
       </c>
@@ -3849,7 +3859,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D24" s="9" t="s">
         <v>23</v>
       </c>
@@ -3867,7 +3877,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="58" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:9" ht="75" x14ac:dyDescent="0.25">
       <c r="D25" s="9" t="s">
         <v>23</v>
       </c>
@@ -3885,7 +3895,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D26" s="9" t="s">
         <v>23</v>
       </c>
@@ -3903,7 +3913,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D27" s="9" t="s">
         <v>23</v>
       </c>
@@ -3921,7 +3931,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D28" s="9" t="s">
         <v>23</v>
       </c>
@@ -3939,7 +3949,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="29" spans="2:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D29" s="9" t="s">
         <v>23</v>
       </c>
@@ -3957,7 +3967,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="30" spans="2:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D30" s="9" t="s">
         <v>23</v>
       </c>
@@ -3975,7 +3985,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="31" spans="2:9" ht="58" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:9" ht="60" x14ac:dyDescent="0.25">
       <c r="D31" s="9" t="s">
         <v>23</v>
       </c>
@@ -3993,7 +4003,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="32" spans="2:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D32" s="9" t="s">
         <v>23</v>
       </c>
@@ -4011,7 +4021,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="33" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="4:9" ht="60" x14ac:dyDescent="0.25">
       <c r="D33" s="9" t="s">
         <v>23</v>
       </c>
@@ -4029,7 +4039,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="34" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D34" s="9" t="s">
         <v>23</v>
       </c>
@@ -4047,7 +4057,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="35" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D35" s="9" t="s">
         <v>23</v>
       </c>
@@ -4065,7 +4075,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="36" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D36" s="9" t="s">
         <v>23</v>
       </c>
@@ -4083,7 +4093,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="37" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D37" s="9" t="s">
         <v>23</v>
       </c>
@@ -4101,7 +4111,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="38" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="38" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D38" s="9" t="s">
         <v>23</v>
       </c>
@@ -4119,7 +4129,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="39" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="39" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D39" s="9" t="s">
         <v>23</v>
       </c>
@@ -4137,7 +4147,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="40" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="40" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D40" s="9" t="s">
         <v>23</v>
       </c>
@@ -4155,7 +4165,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="41" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="41" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D41" s="9" t="s">
         <v>23</v>
       </c>
@@ -4173,7 +4183,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="42" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="42" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D42" s="9" t="s">
         <v>23</v>
       </c>
@@ -4191,7 +4201,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="43" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D43" s="9" t="s">
         <v>23</v>
       </c>
@@ -4209,7 +4219,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="44" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="44" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D44" s="9" t="s">
         <v>23</v>
       </c>
@@ -4227,7 +4237,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="45" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="45" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D45" s="9" t="s">
         <v>23</v>
       </c>
@@ -4245,7 +4255,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="46" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="4:9" ht="60" x14ac:dyDescent="0.25">
       <c r="D46" s="9" t="s">
         <v>23</v>
       </c>
@@ -4263,7 +4273,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="47" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="47" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D47" s="9" t="s">
         <v>23</v>
       </c>
@@ -4281,7 +4291,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="48" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="48" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D48" s="9" t="s">
         <v>23</v>
       </c>
@@ -4299,7 +4309,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="49" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="49" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D49" s="9" t="s">
         <v>23</v>
       </c>
@@ -4317,7 +4327,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="50" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="50" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D50" s="9" t="s">
         <v>23</v>
       </c>
@@ -4335,7 +4345,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="51" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D51" s="9" t="s">
         <v>23</v>
       </c>
@@ -4353,7 +4363,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="52" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D52" s="9" t="s">
         <v>23</v>
       </c>
@@ -4371,7 +4381,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="53" spans="4:9" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="4:9" ht="75" x14ac:dyDescent="0.25">
       <c r="D53" s="9" t="s">
         <v>23</v>
       </c>
@@ -4389,7 +4399,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="54" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D54" s="9" t="s">
         <v>23</v>
       </c>
@@ -4407,7 +4417,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="55" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="4:9" ht="60" x14ac:dyDescent="0.25">
       <c r="D55" s="9" t="s">
         <v>23</v>
       </c>
@@ -4425,7 +4435,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="56" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D56" s="9" t="s">
         <v>44</v>
       </c>
@@ -4443,7 +4453,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="57" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D57" s="9" t="s">
         <v>44</v>
       </c>
@@ -4461,7 +4471,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="58" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="58" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D58" s="9" t="s">
         <v>18</v>
       </c>
@@ -4479,7 +4489,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="59" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D59" s="9" t="s">
         <v>18</v>
       </c>
@@ -4497,7 +4507,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="60" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D60" s="9" t="s">
         <v>18</v>
       </c>
@@ -4515,7 +4525,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="61" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D61" s="9" t="s">
         <v>18</v>
       </c>
@@ -4533,7 +4543,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="62" spans="4:9" ht="58" x14ac:dyDescent="0.35">
+    <row r="62" spans="4:9" ht="60" x14ac:dyDescent="0.25">
       <c r="D62" s="9" t="s">
         <v>18</v>
       </c>
@@ -4551,7 +4561,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="63" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="63" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D63" s="9" t="s">
         <v>10</v>
       </c>
@@ -4569,7 +4579,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="64" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="64" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D64" s="9" t="s">
         <v>10</v>
       </c>
@@ -4587,7 +4597,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="65" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="65" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D65" s="9" t="s">
         <v>10</v>
       </c>
@@ -4605,7 +4615,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="66" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="66" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D66" s="9" t="s">
         <v>10</v>
       </c>
@@ -4623,7 +4633,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="67" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D67" s="9" t="s">
         <v>10</v>
       </c>
@@ -4641,7 +4651,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="68" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D68" s="9" t="s">
         <v>10</v>
       </c>
@@ -4659,7 +4669,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="69" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D69" s="9" t="s">
         <v>10</v>
       </c>
@@ -4677,7 +4687,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="70" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="70" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D70" s="9" t="s">
         <v>10</v>
       </c>
@@ -4695,7 +4705,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="71" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="71" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D71" s="9" t="s">
         <v>10</v>
       </c>
@@ -4713,7 +4723,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="72" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D72" s="9" t="s">
         <v>10</v>
       </c>
@@ -4731,7 +4741,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="73" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="73" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D73" s="9" t="s">
         <v>21</v>
       </c>
@@ -4749,7 +4759,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="74" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="74" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D74" s="9" t="s">
         <v>32</v>
       </c>
@@ -4767,7 +4777,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="75" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="75" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D75" s="9" t="s">
         <v>16</v>
       </c>
@@ -4785,7 +4795,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="76" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="76" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D76" s="9" t="s">
         <v>16</v>
       </c>
@@ -4803,7 +4813,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="77" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D77" s="9" t="s">
         <v>16</v>
       </c>
@@ -4821,7 +4831,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="78" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D78" s="9" t="s">
         <v>16</v>
       </c>
@@ -4839,7 +4849,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="79" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="79" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D79" s="9" t="s">
         <v>42</v>
       </c>
@@ -4857,7 +4867,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="80" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="80" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D80" s="9" t="s">
         <v>42</v>
       </c>
@@ -4875,7 +4885,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="81" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="81" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D81" s="9" t="s">
         <v>14</v>
       </c>
@@ -4893,7 +4903,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="82" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D82" s="9" t="s">
         <v>14</v>
       </c>
@@ -4911,7 +4921,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="83" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D83" s="9" t="s">
         <v>14</v>
       </c>
@@ -4929,7 +4939,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="84" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="84" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D84" s="9" t="s">
         <v>14</v>
       </c>
@@ -4947,7 +4957,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="85" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D85" s="9" t="s">
         <v>40</v>
       </c>
@@ -4965,7 +4975,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="86" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D86" s="9" t="s">
         <v>40</v>
       </c>
@@ -4983,7 +4993,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="87" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="87" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D87" s="9" t="s">
         <v>148</v>
       </c>
@@ -5001,7 +5011,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="88" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="88" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D88" s="9" t="s">
         <v>148</v>
       </c>
@@ -5019,7 +5029,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="89" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="89" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D89" s="9" t="s">
         <v>36</v>
       </c>
@@ -5037,7 +5047,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="90" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D90" s="9" t="s">
         <v>36</v>
       </c>
@@ -5055,7 +5065,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="91" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="4:9" ht="60" x14ac:dyDescent="0.25">
       <c r="D91" s="9" t="s">
         <v>36</v>
       </c>
@@ -5072,7 +5082,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="92" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D92" s="9" t="s">
         <v>36</v>
       </c>
@@ -5089,7 +5099,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="93" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D93" s="9" t="s">
         <v>36</v>
       </c>
@@ -5106,7 +5116,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="94" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D94" s="9" t="s">
         <v>36</v>
       </c>
@@ -5123,7 +5133,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="95" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D95" s="9" t="s">
         <v>149</v>
       </c>
@@ -5140,7 +5150,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="96" spans="4:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="96" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D96" s="9" t="s">
         <v>149</v>
       </c>
@@ -5157,7 +5167,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="97" spans="7:9" x14ac:dyDescent="0.35">
+    <row r="97" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G97" s="21" t="s">
         <v>63</v>
       </c>
@@ -5168,7 +5178,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="98" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G98" s="21" t="s">
         <v>63</v>
       </c>
@@ -5179,7 +5189,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="99" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G99" s="21" t="s">
         <v>66</v>
       </c>
@@ -5190,7 +5200,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="100" spans="7:9" x14ac:dyDescent="0.35">
+    <row r="100" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G100" s="21" t="s">
         <v>66</v>
       </c>
@@ -5201,7 +5211,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="101" spans="7:9" x14ac:dyDescent="0.35">
+    <row r="101" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G101" s="21" t="s">
         <v>66</v>
       </c>
@@ -5212,7 +5222,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="102" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G102" s="21" t="s">
         <v>66</v>
       </c>
@@ -5223,7 +5233,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="103" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G103" s="21" t="s">
         <v>66</v>
       </c>
@@ -5234,7 +5244,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="104" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="7:9" ht="60" x14ac:dyDescent="0.25">
       <c r="G104" s="21" t="s">
         <v>66</v>
       </c>
@@ -5245,7 +5255,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="105" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G105" s="21" t="s">
         <v>66</v>
       </c>
@@ -5256,7 +5266,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="106" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G106" s="21" t="s">
         <v>66</v>
       </c>
@@ -5267,7 +5277,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="107" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G107" s="21" t="s">
         <v>66</v>
       </c>
@@ -5278,7 +5288,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="108" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="108" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G108" s="21" t="s">
         <v>66</v>
       </c>
@@ -5289,7 +5299,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="109" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="109" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G109" s="21" t="s">
         <v>66</v>
       </c>
@@ -5300,7 +5310,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="110" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G110" s="21" t="s">
         <v>66</v>
       </c>
@@ -5311,7 +5321,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="111" spans="7:9" x14ac:dyDescent="0.35">
+    <row r="111" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G111" s="21" t="s">
         <v>66</v>
       </c>
@@ -5322,7 +5332,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="112" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G112" s="21" t="s">
         <v>68</v>
       </c>
@@ -5333,7 +5343,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="113" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="7:9" ht="60" x14ac:dyDescent="0.25">
       <c r="G113" s="21" t="s">
         <v>73</v>
       </c>
@@ -5344,7 +5354,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="114" spans="7:9" x14ac:dyDescent="0.35">
+    <row r="114" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G114" s="21" t="s">
         <v>73</v>
       </c>
@@ -5355,7 +5365,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="115" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="115" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G115" s="21" t="s">
         <v>73</v>
       </c>
@@ -5366,7 +5376,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="116" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="116" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G116" s="21" t="s">
         <v>377</v>
       </c>
@@ -5377,7 +5387,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="117" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="117" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G117" s="21" t="s">
         <v>75</v>
       </c>
@@ -5388,7 +5398,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="118" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="118" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G118" s="21" t="s">
         <v>75</v>
       </c>
@@ -5399,7 +5409,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="119" spans="7:9" x14ac:dyDescent="0.35">
+    <row r="119" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G119" s="21" t="s">
         <v>75</v>
       </c>
@@ -5410,7 +5420,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="120" spans="7:9" x14ac:dyDescent="0.35">
+    <row r="120" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G120" s="21" t="s">
         <v>75</v>
       </c>
@@ -5421,7 +5431,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="121" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="121" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G121" s="21" t="s">
         <v>75</v>
       </c>
@@ -5432,7 +5442,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="122" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="7:9" ht="60" x14ac:dyDescent="0.25">
       <c r="G122" s="21" t="s">
         <v>75</v>
       </c>
@@ -5443,7 +5453,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="123" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G123" s="21" t="s">
         <v>75</v>
       </c>
@@ -5454,7 +5464,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="124" spans="7:9" ht="58" x14ac:dyDescent="0.35">
+    <row r="124" spans="7:9" ht="75" x14ac:dyDescent="0.25">
       <c r="G124" s="21" t="s">
         <v>75</v>
       </c>
@@ -5465,7 +5475,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="125" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="125" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G125" s="21" t="s">
         <v>75</v>
       </c>
@@ -5476,7 +5486,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="126" spans="7:9" ht="58" x14ac:dyDescent="0.35">
+    <row r="126" spans="7:9" ht="75" x14ac:dyDescent="0.25">
       <c r="G126" s="21" t="s">
         <v>75</v>
       </c>
@@ -5487,7 +5497,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="127" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="127" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G127" s="21" t="s">
         <v>75</v>
       </c>
@@ -5498,7 +5508,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="128" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="128" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G128" s="21" t="s">
         <v>75</v>
       </c>
@@ -5509,7 +5519,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="129" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="129" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G129" s="21" t="s">
         <v>75</v>
       </c>
@@ -5520,7 +5530,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="130" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="130" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G130" s="21" t="s">
         <v>75</v>
       </c>
@@ -5531,7 +5541,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="131" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="131" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G131" s="21" t="s">
         <v>75</v>
       </c>
@@ -5542,7 +5552,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="132" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="132" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G132" s="21" t="s">
         <v>75</v>
       </c>
@@ -5553,7 +5563,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="133" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="133" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G133" s="21" t="s">
         <v>75</v>
       </c>
@@ -5564,7 +5574,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="134" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="134" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G134" s="21" t="s">
         <v>75</v>
       </c>
@@ -5575,7 +5585,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="135" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="135" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G135" s="21" t="s">
         <v>75</v>
       </c>
@@ -5586,7 +5596,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="136" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="136" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G136" s="21" t="s">
         <v>75</v>
       </c>
@@ -5597,7 +5607,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="137" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="137" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G137" s="21" t="s">
         <v>75</v>
       </c>
@@ -5608,7 +5618,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="138" spans="7:9" x14ac:dyDescent="0.35">
+    <row r="138" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G138" s="21" t="s">
         <v>75</v>
       </c>
@@ -5619,7 +5629,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="139" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="139" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G139" s="21" t="s">
         <v>75</v>
       </c>
@@ -5630,7 +5640,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="140" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="140" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G140" s="21" t="s">
         <v>75</v>
       </c>
@@ -5641,7 +5651,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="141" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="141" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G141" s="21" t="s">
         <v>75</v>
       </c>
@@ -5652,7 +5662,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="142" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G142" s="21" t="s">
         <v>75</v>
       </c>
@@ -5663,7 +5673,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="143" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="143" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G143" s="21" t="s">
         <v>75</v>
       </c>
@@ -5674,7 +5684,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="144" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="144" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G144" s="21" t="s">
         <v>75</v>
       </c>
@@ -5685,7 +5695,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="145" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="145" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G145" s="21" t="s">
         <v>75</v>
       </c>
@@ -5696,7 +5706,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="146" spans="7:9" ht="58" x14ac:dyDescent="0.35">
+    <row r="146" spans="7:9" ht="60" x14ac:dyDescent="0.25">
       <c r="G146" s="21" t="s">
         <v>75</v>
       </c>
@@ -5707,7 +5717,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="147" spans="7:9" x14ac:dyDescent="0.35">
+    <row r="147" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G147" s="21" t="s">
         <v>79</v>
       </c>
@@ -5718,7 +5728,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="148" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="148" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G148" s="21" t="s">
         <v>79</v>
       </c>
@@ -5729,7 +5739,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="149" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="149" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G149" s="21" t="s">
         <v>444</v>
       </c>
@@ -5740,7 +5750,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="150" spans="7:9" x14ac:dyDescent="0.35">
+    <row r="150" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G150" s="21" t="s">
         <v>444</v>
       </c>
@@ -5751,7 +5761,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="151" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="151" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G151" s="21" t="s">
         <v>84</v>
       </c>
@@ -5762,7 +5772,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="152" spans="7:9" x14ac:dyDescent="0.35">
+    <row r="152" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G152" s="21" t="s">
         <v>451</v>
       </c>
@@ -5773,7 +5783,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="153" spans="7:9" x14ac:dyDescent="0.35">
+    <row r="153" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G153" s="21" t="s">
         <v>454</v>
       </c>
@@ -5784,7 +5794,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="154" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="154" spans="7:9" ht="60" x14ac:dyDescent="0.25">
       <c r="G154" s="21" t="s">
         <v>454</v>
       </c>
@@ -5795,7 +5805,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="155" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="155" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G155" s="21" t="s">
         <v>104</v>
       </c>
@@ -5806,7 +5816,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="156" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="156" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G156" s="21" t="s">
         <v>104</v>
       </c>
@@ -5817,7 +5827,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="157" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="157" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G157" s="21" t="s">
         <v>104</v>
       </c>
@@ -5828,7 +5838,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="158" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="158" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G158" s="21" t="s">
         <v>104</v>
       </c>
@@ -5839,7 +5849,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="159" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="159" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G159" s="21" t="s">
         <v>104</v>
       </c>
@@ -5850,7 +5860,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="160" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="160" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G160" s="21" t="s">
         <v>104</v>
       </c>
@@ -5861,7 +5871,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="161" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="161" spans="7:9" ht="60" x14ac:dyDescent="0.25">
       <c r="G161" s="21" t="s">
         <v>104</v>
       </c>
@@ -5872,7 +5882,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="162" spans="7:9" ht="58" x14ac:dyDescent="0.35">
+    <row r="162" spans="7:9" ht="60" x14ac:dyDescent="0.25">
       <c r="G162" s="21" t="s">
         <v>104</v>
       </c>
@@ -5883,7 +5893,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="163" spans="7:9" ht="58" x14ac:dyDescent="0.35">
+    <row r="163" spans="7:9" ht="60" x14ac:dyDescent="0.25">
       <c r="G163" s="21" t="s">
         <v>104</v>
       </c>
@@ -5894,7 +5904,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="164" spans="7:9" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="164" spans="7:9" ht="75" x14ac:dyDescent="0.25">
       <c r="G164" s="21" t="s">
         <v>104</v>
       </c>
@@ -5905,7 +5915,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="165" spans="7:9" ht="58" x14ac:dyDescent="0.35">
+    <row r="165" spans="7:9" ht="60" x14ac:dyDescent="0.25">
       <c r="G165" s="21" t="s">
         <v>104</v>
       </c>
@@ -5916,7 +5926,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="166" spans="7:9" x14ac:dyDescent="0.35">
+    <row r="166" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G166" s="21" t="s">
         <v>104</v>
       </c>
@@ -5927,7 +5937,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="167" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="167" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G167" s="21" t="s">
         <v>104</v>
       </c>
@@ -5938,7 +5948,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="168" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="168" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G168" s="21" t="s">
         <v>104</v>
       </c>
@@ -5949,7 +5959,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="169" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="169" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G169" s="21" t="s">
         <v>104</v>
       </c>
@@ -5960,7 +5970,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="170" spans="7:9" ht="58" x14ac:dyDescent="0.35">
+    <row r="170" spans="7:9" ht="60" x14ac:dyDescent="0.25">
       <c r="G170" s="21" t="s">
         <v>104</v>
       </c>
@@ -5971,7 +5981,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="171" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="171" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G171" s="21" t="s">
         <v>104</v>
       </c>
@@ -5982,7 +5992,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="172" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="172" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G172" s="21" t="s">
         <v>104</v>
       </c>
@@ -5993,7 +6003,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="173" spans="7:9" ht="58" x14ac:dyDescent="0.35">
+    <row r="173" spans="7:9" ht="60" x14ac:dyDescent="0.25">
       <c r="G173" s="21" t="s">
         <v>104</v>
       </c>
@@ -6004,7 +6014,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="174" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="174" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G174" s="21" t="s">
         <v>104</v>
       </c>
@@ -6015,7 +6025,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="175" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="175" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G175" s="21" t="s">
         <v>104</v>
       </c>
@@ -6026,7 +6036,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="176" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="176" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G176" s="21" t="s">
         <v>104</v>
       </c>
@@ -6037,7 +6047,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="177" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="177" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G177" s="21" t="s">
         <v>104</v>
       </c>
@@ -6048,7 +6058,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="178" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="178" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G178" s="21" t="s">
         <v>104</v>
       </c>
@@ -6059,7 +6069,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="179" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="179" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G179" s="21" t="s">
         <v>104</v>
       </c>
@@ -6070,7 +6080,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="180" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="180" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G180" s="21" t="s">
         <v>104</v>
       </c>
@@ -6081,7 +6091,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="181" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="181" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G181" s="21" t="s">
         <v>104</v>
       </c>
@@ -6092,7 +6102,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="182" spans="7:9" ht="58" x14ac:dyDescent="0.35">
+    <row r="182" spans="7:9" ht="60" x14ac:dyDescent="0.25">
       <c r="G182" s="21" t="s">
         <v>104</v>
       </c>
@@ -6103,7 +6113,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="183" spans="7:9" ht="58" x14ac:dyDescent="0.35">
+    <row r="183" spans="7:9" ht="60" x14ac:dyDescent="0.25">
       <c r="G183" s="21" t="s">
         <v>105</v>
       </c>
@@ -6114,7 +6124,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="184" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="184" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G184" s="21" t="s">
         <v>105</v>
       </c>
@@ -6125,7 +6135,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="185" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="185" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G185" s="21" t="s">
         <v>105</v>
       </c>
@@ -6136,7 +6146,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="186" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="186" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G186" s="21" t="s">
         <v>105</v>
       </c>
@@ -6147,7 +6157,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="187" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="187" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G187" s="21" t="s">
         <v>106</v>
       </c>
@@ -6158,7 +6168,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="188" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="188" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G188" s="21" t="s">
         <v>106</v>
       </c>
@@ -6169,7 +6179,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="189" spans="7:9" x14ac:dyDescent="0.35">
+    <row r="189" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G189" s="21" t="s">
         <v>106</v>
       </c>
@@ -6180,7 +6190,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="190" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="190" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G190" s="21" t="s">
         <v>106</v>
       </c>
@@ -6191,7 +6201,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="191" spans="7:9" x14ac:dyDescent="0.35">
+    <row r="191" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G191" s="21" t="s">
         <v>106</v>
       </c>
@@ -6202,7 +6212,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="192" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="192" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G192" s="21" t="s">
         <v>106</v>
       </c>
@@ -6213,7 +6223,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="193" spans="7:9" x14ac:dyDescent="0.35">
+    <row r="193" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G193" s="21" t="s">
         <v>106</v>
       </c>
@@ -6224,7 +6234,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="194" spans="7:9" x14ac:dyDescent="0.35">
+    <row r="194" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G194" s="21" t="s">
         <v>106</v>
       </c>
@@ -6235,7 +6245,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="195" spans="7:9" x14ac:dyDescent="0.35">
+    <row r="195" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G195" s="21" t="s">
         <v>106</v>
       </c>
@@ -6246,7 +6256,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="196" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="196" spans="7:9" ht="60" x14ac:dyDescent="0.25">
       <c r="G196" s="21" t="s">
         <v>106</v>
       </c>
@@ -6257,7 +6267,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="197" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="197" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G197" s="21" t="s">
         <v>109</v>
       </c>
@@ -6268,7 +6278,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="198" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="198" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G198" s="21" t="s">
         <v>109</v>
       </c>
@@ -6279,7 +6289,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="199" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="199" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G199" s="21" t="s">
         <v>109</v>
       </c>
@@ -6290,7 +6300,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="200" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="200" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G200" s="21" t="s">
         <v>109</v>
       </c>
@@ -6301,7 +6311,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="201" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="201" spans="7:9" ht="60" x14ac:dyDescent="0.25">
       <c r="G201" s="21" t="s">
         <v>109</v>
       </c>
@@ -6312,7 +6322,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="202" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="202" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G202" s="21" t="s">
         <v>109</v>
       </c>
@@ -6323,7 +6333,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="203" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="203" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G203" s="21" t="s">
         <v>109</v>
       </c>
@@ -6334,7 +6344,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="204" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="204" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G204" s="21" t="s">
         <v>109</v>
       </c>
@@ -6345,7 +6355,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="205" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="205" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G205" s="21" t="s">
         <v>111</v>
       </c>
@@ -6356,7 +6366,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="206" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="206" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G206" s="21" t="s">
         <v>111</v>
       </c>
@@ -6367,7 +6377,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="207" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="207" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G207" s="21" t="s">
         <v>111</v>
       </c>
@@ -6378,7 +6388,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="208" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="208" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G208" s="21" t="s">
         <v>114</v>
       </c>
@@ -6389,7 +6399,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="209" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="209" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G209" s="21" t="s">
         <v>114</v>
       </c>
@@ -6400,7 +6410,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="210" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="210" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G210" s="21" t="s">
         <v>114</v>
       </c>
@@ -6411,7 +6421,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="211" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="211" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G211" s="21" t="s">
         <v>114</v>
       </c>
@@ -6422,7 +6432,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="212" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="212" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G212" s="21" t="s">
         <v>114</v>
       </c>
@@ -6433,7 +6443,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="213" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="213" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G213" s="21" t="s">
         <v>114</v>
       </c>
@@ -6444,7 +6454,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="214" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="214" spans="7:9" ht="60" x14ac:dyDescent="0.25">
       <c r="G214" s="21" t="s">
         <v>114</v>
       </c>
@@ -6455,7 +6465,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="215" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="215" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G215" s="21" t="s">
         <v>114</v>
       </c>
@@ -6466,7 +6476,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="216" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="216" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G216" s="21" t="s">
         <v>114</v>
       </c>
@@ -6477,7 +6487,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="217" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="217" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G217" s="21" t="s">
         <v>114</v>
       </c>
@@ -6488,7 +6498,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="218" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="218" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G218" s="21" t="s">
         <v>114</v>
       </c>
@@ -6499,7 +6509,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="219" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="219" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G219" s="21" t="s">
         <v>114</v>
       </c>
@@ -6510,7 +6520,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="220" spans="7:9" x14ac:dyDescent="0.35">
+    <row r="220" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G220" s="21" t="s">
         <v>114</v>
       </c>
@@ -6521,7 +6531,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="221" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="221" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G221" s="21" t="s">
         <v>114</v>
       </c>
@@ -6532,7 +6542,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="222" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="222" spans="7:9" ht="60" x14ac:dyDescent="0.25">
       <c r="G222" s="21" t="s">
         <v>114</v>
       </c>
@@ -6543,7 +6553,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="223" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="223" spans="7:9" ht="60" x14ac:dyDescent="0.25">
       <c r="G223" s="21" t="s">
         <v>114</v>
       </c>
@@ -6554,7 +6564,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="224" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="224" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G224" s="21" t="s">
         <v>114</v>
       </c>
@@ -6565,7 +6575,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="225" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="225" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G225" s="21" t="s">
         <v>114</v>
       </c>
@@ -6576,7 +6586,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="226" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="226" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G226" s="21" t="s">
         <v>114</v>
       </c>
@@ -6587,7 +6597,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="227" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="227" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G227" s="21" t="s">
         <v>114</v>
       </c>
@@ -6598,7 +6608,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="228" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="228" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G228" s="21" t="s">
         <v>114</v>
       </c>
@@ -6609,7 +6619,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="229" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="229" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G229" s="21" t="s">
         <v>114</v>
       </c>
@@ -6620,7 +6630,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="230" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="230" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G230" s="21" t="s">
         <v>114</v>
       </c>
@@ -6631,7 +6641,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="231" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="231" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G231" s="21" t="s">
         <v>115</v>
       </c>
@@ -6642,7 +6652,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="232" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="232" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G232" s="21" t="s">
         <v>115</v>
       </c>
@@ -6653,7 +6663,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="233" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="233" spans="7:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G233" s="21" t="s">
         <v>115</v>
       </c>
@@ -6664,7 +6674,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="234" spans="7:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="234" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G234" s="21" t="s">
         <v>115</v>
       </c>
@@ -6675,7 +6685,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="235" spans="7:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="235" spans="7:9" ht="45" x14ac:dyDescent="0.25">
       <c r="G235" s="21" t="s">
         <v>115</v>
       </c>
